--- a/excel/12日期函数.xlsx
+++ b/excel/12日期函数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10830"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2B6A78-0ED6-974B-B2F5-0257A12B97AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9286B4-2A79-0C40-9833-207671F66A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/excel/12日期函数.xlsx
+++ b/excel/12日期函数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9286B4-2A79-0C40-9833-207671F66A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0CD25F-30AC-1D4E-9346-5FA3508EEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,18 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
   <si>
     <t>一、</t>
   </si>
   <si>
     <t>认识时间和日期</t>
-  </si>
-  <si>
-    <t>结果对应小时数折算成天的数值 同理小时数与分钟数一样 本质上是一个换算过程</t>
-  </si>
-  <si>
-    <t>整数单元格格式如果是日期 则从1900年开始计算 注意格式转换</t>
   </si>
   <si>
     <t>二、</t>
@@ -167,10 +161,6 @@
     <t>持续时间(分钟)</t>
   </si>
   <si>
-    <t>Excel把整数1定义为1天（24小时）使用整数/24代表1天的小时数数值</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>1、Year、Month、Day、Today函数</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -231,6 +221,22 @@
   </si>
   <si>
     <t>返回某个月份最后一天的序列号</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>在Excel中日期和时间是数值的一种特殊格式  默认使用1900日期系统即数值1表示1900年1月1日</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010年1月1日的日期序列值为40179表示从1900年1月1日起的第40179天</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间不足1天的小数部分 根据时间的进制1天共分为24小时 因而1小时的数值大小为1/24</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>同理1分钟的数值为1/1440 1秒的数值为1/86400</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -746,93 +752,95 @@
     </row>
     <row r="5" spans="1:5" s="9" customFormat="1" ht="14">
       <c r="C5" s="18" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" s="9" customFormat="1" ht="14">
       <c r="C6" s="18" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" s="9" customFormat="1" ht="14">
       <c r="C7" s="18" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" s="9" customFormat="1" ht="14">
-      <c r="C8" s="18"/>
+      <c r="C8" s="18" t="s">
+        <v>59</v>
+      </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
     </row>
-    <row r="9" spans="1:5" s="9" customFormat="1" ht="14">
-      <c r="C9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-    </row>
+    <row r="9" spans="1:5" s="9" customFormat="1" ht="14"/>
     <row r="10" spans="1:5" s="9" customFormat="1" ht="14">
-      <c r="C10" s="19">
+      <c r="C10" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" s="9" customFormat="1" ht="14">
+      <c r="C11" s="19">
         <v>1</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D11" s="20">
         <v>2958465</v>
       </c>
-      <c r="E10" s="18"/>
-    </row>
-    <row r="11" spans="1:5" s="9" customFormat="1" ht="14">
-      <c r="C11" s="18">
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" s="9" customFormat="1" ht="14">
+      <c r="C12" s="18">
         <v>1</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D12" s="18">
         <v>2958465</v>
       </c>
-      <c r="E11" s="21">
-        <f>D11+1</f>
+      <c r="E12" s="21">
+        <f>D12+1</f>
         <v>2958466</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="9" customFormat="1" ht="14"/>
     <row r="13" spans="1:5" s="9" customFormat="1" ht="14"/>
     <row r="14" spans="1:5" s="9" customFormat="1" ht="14">
       <c r="A14" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="9" customFormat="1" ht="14"/>
     <row r="16" spans="1:5" s="9" customFormat="1" ht="14">
       <c r="B16" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="9" customFormat="1" ht="14">
       <c r="C17" s="18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="9" customFormat="1" ht="14"/>
     <row r="19" spans="1:8" s="9" customFormat="1">
       <c r="B19" s="9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:8" s="9" customFormat="1">
       <c r="C20" s="18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G20" s="13"/>
     </row>
@@ -841,55 +849,55 @@
     </row>
     <row r="22" spans="1:8" s="9" customFormat="1">
       <c r="B22" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" s="9" customFormat="1">
       <c r="C23" s="22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:8" s="9" customFormat="1">
       <c r="B24"/>
       <c r="C24" s="23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G24" s="13"/>
     </row>
     <row r="25" spans="1:8" s="9" customFormat="1">
       <c r="B25"/>
       <c r="C25" s="23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:8" s="9" customFormat="1">
       <c r="B26"/>
       <c r="C26" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G26" s="13"/>
     </row>
     <row r="27" spans="1:8" s="9" customFormat="1">
       <c r="B27"/>
       <c r="C27" s="23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G27" s="13"/>
     </row>
     <row r="28" spans="1:8" s="9" customFormat="1">
       <c r="B28"/>
       <c r="C28" s="23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="9" customFormat="1">
       <c r="B29"/>
       <c r="C29" s="23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -901,7 +909,7 @@
     <row r="31" spans="1:8">
       <c r="A31" s="9"/>
       <c r="B31" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C31" s="9"/>
     </row>
@@ -909,13 +917,13 @@
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H32" s="9"/>
     </row>
     <row r="33" spans="2:6">
       <c r="C33" s="23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33"/>
@@ -926,7 +934,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E34"/>
       <c r="F34"/>
@@ -936,19 +944,19 @@
         <v>2</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E35"/>
       <c r="F35"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="2:6">
       <c r="C38" s="18" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="2:6">
@@ -956,48 +964,48 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="9"/>
       <c r="C41" s="18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="2:6">
       <c r="C42" s="18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="2:6">
       <c r="C43" s="18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="C46" s="18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="C47" s="18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="C48" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" s="18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1723,37 +1731,37 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>22</v>
-      </c>
       <c r="I1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="17" t="s">
+      <c r="M1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="N1" s="17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
@@ -1848,36 +1856,36 @@
       <c r="F5"/>
       <c r="G5"/>
       <c r="I5" s="17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="17" t="s">
-        <v>30</v>
-      </c>
       <c r="M5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="17" t="s">
         <v>31</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>19</v>
-      </c>
       <c r="C6" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6"/>
       <c r="I6" s="2">
@@ -1980,10 +1988,10 @@
       </c>
       <c r="G9"/>
       <c r="M9" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -2005,13 +2013,13 @@
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>22</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -2044,17 +2052,17 @@
         <v>41219</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G13"/>
       <c r="M13" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -2076,13 +2084,13 @@
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>22</v>
-      </c>
       <c r="C15" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E15" s="4">
         <v>41129</v>
@@ -2137,10 +2145,10 @@
       </c>
       <c r="G17"/>
       <c r="M17" s="17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1">

--- a/excel/12日期函数.xlsx
+++ b/excel/12日期函数.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11011"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0CD25F-30AC-1D4E-9346-5FA3508EEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFE35CB-1977-DF40-B0FC-D37D232F4553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="708" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t>一、</t>
   </si>
@@ -237,6 +237,10 @@
   </si>
   <si>
     <t>同理1分钟的数值为1/1440 1秒的数值为1/86400</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>取整数部分</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -244,11 +248,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="h:mm;@"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="178" formatCode="[$-804]aaa;@"/>
     <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="182" formatCode="yyyy/m/d\ h:mm;@"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -358,7 +363,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -420,6 +425,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1018,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" style="3" customWidth="1"/>
@@ -1033,7 +1039,10 @@
     <col min="12" max="12" width="9" style="3"/>
     <col min="13" max="13" width="9.5" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="214" width="9" style="3"/>
+    <col min="15" max="15" width="9" style="3"/>
+    <col min="16" max="16" width="15.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="214" width="9" style="3"/>
     <col min="215" max="215" width="3" style="3" customWidth="1"/>
     <col min="216" max="216" width="12.1640625" style="3" customWidth="1"/>
     <col min="217" max="217" width="9.6640625" style="3" customWidth="1"/>
@@ -1729,7 +1738,7 @@
     <col min="16104" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1">
+    <row r="1" spans="1:17" ht="15" customHeight="1">
       <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
@@ -1763,8 +1772,14 @@
       <c r="N1" s="17" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1">
+      <c r="P1" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15" customHeight="1">
       <c r="A2" s="6">
         <v>0.375</v>
       </c>
@@ -1802,8 +1817,16 @@
         <f>"第"&amp;WEEKDAY(M2,2)&amp;"周"</f>
         <v>第6周</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1">
+      <c r="P2" s="25">
+        <f ca="1">NOW()</f>
+        <v>46313.949780555558</v>
+      </c>
+      <c r="Q2" s="2">
+        <f ca="1">INT(P2)</f>
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15" customHeight="1">
       <c r="A3" s="6">
         <v>0.51388888888888895</v>
       </c>
@@ -1830,7 +1853,7 @@
       <c r="M3"/>
       <c r="N3"/>
     </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1">
+    <row r="4" spans="1:17" ht="15" customHeight="1">
       <c r="A4" s="6">
         <v>0.77777777777777801</v>
       </c>
@@ -1851,7 +1874,7 @@
       <c r="M4"/>
       <c r="N4"/>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1">
+    <row r="5" spans="1:17" ht="15" customHeight="1">
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5"/>
@@ -1871,7 +1894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1">
+    <row r="6" spans="1:17" ht="15" customHeight="1">
       <c r="A6" s="16" t="s">
         <v>15</v>
       </c>
@@ -1906,7 +1929,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1">
+    <row r="7" spans="1:17" ht="15" customHeight="1">
       <c r="A7" s="6">
         <v>0.375</v>
       </c>
@@ -1936,7 +1959,7 @@
         <v>4年9月5天</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1">
+    <row r="8" spans="1:17" ht="15" customHeight="1">
       <c r="A8" s="6">
         <v>0.51388888888888895</v>
       </c>
@@ -1968,7 +1991,7 @@
       <c r="M8"/>
       <c r="N8"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1">
+    <row r="9" spans="1:17" ht="15" customHeight="1">
       <c r="A9" s="6">
         <v>0.77777777777777801</v>
       </c>
@@ -1994,7 +2017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1">
+    <row r="10" spans="1:17" ht="15" customHeight="1">
       <c r="E10" s="5">
         <v>39855</v>
       </c>
@@ -2011,7 +2034,7 @@
         <v>第6周第11天</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1">
+    <row r="11" spans="1:17" ht="15" customHeight="1">
       <c r="A11" s="16" t="s">
         <v>18</v>
       </c>
@@ -2025,7 +2048,7 @@
       <c r="F11"/>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1">
+    <row r="12" spans="1:17" ht="15" customHeight="1">
       <c r="A12" s="4">
         <v>41441</v>
       </c>
@@ -2040,7 +2063,7 @@
       <c r="F12"/>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1">
+    <row r="13" spans="1:17" ht="15" customHeight="1">
       <c r="A13" s="4">
         <v>41129</v>
       </c>
@@ -2065,7 +2088,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1">
+    <row r="14" spans="1:17" ht="15" customHeight="1">
       <c r="E14" s="4">
         <v>41441</v>
       </c>
@@ -2082,7 +2105,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1">
+    <row r="15" spans="1:17" ht="15" customHeight="1">
       <c r="A15" s="16" t="s">
         <v>18</v>
       </c>
@@ -2103,7 +2126,7 @@
       <c r="I15" s="2"/>
       <c r="J15"/>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1">
+    <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="4">
         <v>41441</v>
       </c>
